--- a/Team-Data/2013-14/2-21-2013-14.xlsx
+++ b/Team-Data/2013-14/2-21-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,52 +728,52 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" t="n">
         <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>0.463</v>
+        <v>0.472</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J2" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0.459</v>
       </c>
       <c r="L2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.374</v>
+        <v>0.373</v>
       </c>
       <c r="O2" t="n">
         <v>16.6</v>
       </c>
       <c r="P2" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.777</v>
+        <v>0.778</v>
       </c>
       <c r="R2" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="S2" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T2" t="n">
         <v>40.7</v>
@@ -715,7 +782,7 @@
         <v>25.5</v>
       </c>
       <c r="V2" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W2" t="n">
         <v>8.800000000000001</v>
@@ -727,49 +794,49 @@
         <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA2" t="n">
         <v>19.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.4</v>
+        <v>101.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG2" t="n">
         <v>17</v>
       </c>
-      <c r="AE2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>18</v>
-      </c>
       <c r="AH2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI2" t="n">
         <v>15</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
         <v>7</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO2" t="n">
         <v>21</v>
@@ -778,7 +845,7 @@
         <v>24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR2" t="n">
         <v>27</v>
@@ -793,7 +860,7 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AW2" t="n">
         <v>5</v>
@@ -814,7 +881,7 @@
         <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E3" t="n">
         <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>0.339</v>
+        <v>0.345</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
@@ -861,49 +928,49 @@
         <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L3" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.328</v>
+        <v>0.331</v>
       </c>
       <c r="O3" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P3" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R3" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S3" t="n">
         <v>31.6</v>
       </c>
       <c r="T3" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U3" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V3" t="n">
         <v>15.5</v>
       </c>
       <c r="W3" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
         <v>4.5</v>
@@ -915,31 +982,31 @@
         <v>18.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.7</v>
+        <v>-3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>24</v>
       </c>
       <c r="AF3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH3" t="n">
         <v>29</v>
       </c>
       <c r="AI3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AK3" t="n">
         <v>26</v>
@@ -963,7 +1030,7 @@
         <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS3" t="n">
         <v>19</v>
@@ -975,13 +1042,13 @@
         <v>26</v>
       </c>
       <c r="AV3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1173,7 @@
         <v>30</v>
       </c>
       <c r="AE4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF4" t="n">
         <v>14</v>
@@ -1115,7 +1182,7 @@
         <v>16</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
@@ -1124,16 +1191,16 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AM4" t="n">
         <v>14</v>
       </c>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO4" t="n">
         <v>9</v>
@@ -1142,7 +1209,7 @@
         <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
@@ -1154,7 +1221,7 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
@@ -1163,19 +1230,19 @@
         <v>12</v>
       </c>
       <c r="AX4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY4" t="n">
         <v>8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA4" t="n">
         <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
         <v>21</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
         <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>0.464</v>
+        <v>0.455</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1225,10 +1292,10 @@
         <v>35.7</v>
       </c>
       <c r="J5" t="n">
-        <v>81.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
@@ -1237,25 +1304,25 @@
         <v>16.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.353</v>
+        <v>0.355</v>
       </c>
       <c r="O5" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="P5" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.723</v>
+        <v>0.724</v>
       </c>
       <c r="R5" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="S5" t="n">
         <v>33.2</v>
       </c>
       <c r="T5" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U5" t="n">
         <v>21.1</v>
@@ -1267,46 +1334,46 @@
         <v>6.2</v>
       </c>
       <c r="X5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y5" t="n">
         <v>5.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB5" t="n">
         <v>95.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ5" t="n">
         <v>24</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL5" t="n">
         <v>29</v>
@@ -1315,10 +1382,10 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP5" t="n">
         <v>7</v>
@@ -1333,7 +1400,7 @@
         <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU5" t="n">
         <v>17</v>
@@ -1345,22 +1412,22 @@
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
         <v>3</v>
       </c>
       <c r="BA5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
         <v>25</v>
       </c>
       <c r="BC5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -1389,58 +1456,58 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
         <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>0.537</v>
+        <v>0.528</v>
       </c>
       <c r="H6" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I6" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="J6" t="n">
         <v>80.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0.428</v>
+        <v>0.427</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M6" t="n">
         <v>17.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.343</v>
+        <v>0.338</v>
       </c>
       <c r="O6" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P6" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R6" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S6" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T6" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U6" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V6" t="n">
         <v>15.7</v>
@@ -1449,7 +1516,7 @@
         <v>7.3</v>
       </c>
       <c r="X6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y6" t="n">
         <v>6.3</v>
@@ -1461,13 +1528,13 @@
         <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.8</v>
+        <v>92.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1479,7 +1546,7 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="n">
         <v>30</v>
@@ -1503,13 +1570,13 @@
         <v>14</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ6" t="n">
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS6" t="n">
         <v>12</v>
@@ -1527,22 +1594,22 @@
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -1571,28 +1638,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" t="n">
         <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
-        <v>0.393</v>
+        <v>0.4</v>
       </c>
       <c r="H7" t="n">
         <v>48.8</v>
       </c>
       <c r="I7" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J7" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.424</v>
+        <v>0.425</v>
       </c>
       <c r="L7" t="n">
         <v>7.1</v>
@@ -1601,25 +1668,25 @@
         <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O7" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P7" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.743</v>
+        <v>0.744</v>
       </c>
       <c r="R7" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S7" t="n">
         <v>31.8</v>
       </c>
       <c r="T7" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="U7" t="n">
         <v>20.3</v>
@@ -1631,7 +1698,7 @@
         <v>7.3</v>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y7" t="n">
         <v>5.9</v>
@@ -1643,16 +1710,16 @@
         <v>20.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC7" t="n">
         <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF7" t="n">
         <v>22</v>
@@ -1664,7 +1731,7 @@
         <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AJ7" t="n">
         <v>5</v>
@@ -1682,16 +1749,16 @@
         <v>15</v>
       </c>
       <c r="AO7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ7" t="n">
         <v>23</v>
       </c>
       <c r="AR7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS7" t="n">
         <v>16</v>
@@ -1709,7 +1776,7 @@
         <v>19</v>
       </c>
       <c r="AX7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AY7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -1753,28 +1820,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
         <v>23</v>
       </c>
       <c r="G8" t="n">
-        <v>0.589</v>
+        <v>0.582</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>39.4</v>
+        <v>39.2</v>
       </c>
       <c r="J8" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.473</v>
+        <v>0.47</v>
       </c>
       <c r="L8" t="n">
         <v>8.300000000000001</v>
@@ -1783,58 +1850,58 @@
         <v>22.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O8" t="n">
         <v>17.2</v>
       </c>
       <c r="P8" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.801</v>
+        <v>0.802</v>
       </c>
       <c r="R8" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="T8" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U8" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="V8" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="W8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y8" t="n">
         <v>3.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA8" t="n">
         <v>19.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.3</v>
+        <v>103.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF8" t="n">
         <v>10</v>
@@ -1849,10 +1916,10 @@
         <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AL8" t="n">
         <v>8</v>
@@ -1864,7 +1931,7 @@
         <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP8" t="n">
         <v>23</v>
@@ -1876,34 +1943,34 @@
         <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT8" t="n">
         <v>28</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW8" t="n">
         <v>6</v>
       </c>
       <c r="AX8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY8" t="n">
         <v>3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA8" t="n">
         <v>23</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -1935,58 +2002,58 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9" t="n">
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G9" t="n">
-        <v>0.463</v>
+        <v>0.472</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J9" t="n">
-        <v>84.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.359</v>
+        <v>0.358</v>
       </c>
       <c r="O9" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P9" t="n">
         <v>26</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.721</v>
+        <v>0.724</v>
       </c>
       <c r="R9" t="n">
         <v>12.3</v>
       </c>
       <c r="S9" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T9" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U9" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="V9" t="n">
         <v>15.5</v>
@@ -2007,22 +2074,22 @@
         <v>21.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.8</v>
+        <v>103.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>-1.8</v>
+        <v>-1.3</v>
       </c>
       <c r="AD9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG9" t="n">
         <v>17</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>18</v>
       </c>
       <c r="AH9" t="n">
         <v>27</v>
@@ -2034,7 +2101,7 @@
         <v>7</v>
       </c>
       <c r="AK9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL9" t="n">
         <v>9</v>
@@ -2061,7 +2128,7 @@
         <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="n">
         <v>13</v>
@@ -2073,7 +2140,7 @@
         <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY9" t="n">
         <v>22</v>
@@ -2088,7 +2155,7 @@
         <v>11</v>
       </c>
       <c r="BC9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -2117,46 +2184,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F10" t="n">
         <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>0.418</v>
+        <v>0.407</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="J10" t="n">
         <v>86.3</v>
       </c>
       <c r="K10" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L10" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
         <v>19.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0.313</v>
+        <v>0.311</v>
       </c>
       <c r="O10" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P10" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="R10" t="n">
         <v>14.6</v>
@@ -2168,13 +2235,13 @@
         <v>45.1</v>
       </c>
       <c r="U10" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="V10" t="n">
         <v>15.2</v>
       </c>
       <c r="W10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X10" t="n">
         <v>5.1</v>
@@ -2186,19 +2253,19 @@
         <v>20.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>100.7</v>
+        <v>100.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.3</v>
+        <v>-2.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
@@ -2207,7 +2274,7 @@
         <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
         <v>7</v>
@@ -2216,7 +2283,7 @@
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>26</v>
@@ -2225,10 +2292,10 @@
         <v>25</v>
       </c>
       <c r="AN10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP10" t="n">
         <v>6</v>
@@ -2240,22 +2307,22 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT10" t="n">
         <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
         <v>16</v>
@@ -2267,10 +2334,10 @@
         <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,7 +2456,7 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI11" t="n">
         <v>5</v>
@@ -2398,19 +2465,19 @@
         <v>6</v>
       </c>
       <c r="AK11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM11" t="n">
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>4.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2571,7 +2638,7 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
         <v>16</v>
@@ -2580,16 +2647,16 @@
         <v>28</v>
       </c>
       <c r="AK12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL12" t="n">
         <v>5</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>4</v>
       </c>
       <c r="AM12" t="n">
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2607,10 +2674,10 @@
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2753,7 +2820,7 @@
         <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
         <v>21</v>
@@ -2771,13 +2838,13 @@
         <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
         <v>4</v>
@@ -2792,22 +2859,22 @@
         <v>4</v>
       </c>
       <c r="AU13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV13" t="n">
         <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY13" t="n">
         <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -2845,55 +2912,55 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" t="n">
         <v>37</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G14" t="n">
-        <v>0.649</v>
+        <v>0.661</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J14" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K14" t="n">
-        <v>0.471</v>
+        <v>0.472</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M14" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="N14" t="n">
         <v>0.343</v>
       </c>
       <c r="O14" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="P14" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.727</v>
+        <v>0.73</v>
       </c>
       <c r="R14" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S14" t="n">
         <v>32.6</v>
       </c>
       <c r="T14" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U14" t="n">
         <v>24</v>
@@ -2905,22 +2972,22 @@
         <v>8.4</v>
       </c>
       <c r="X14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.7</v>
+        <v>106.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
@@ -2938,13 +3005,13 @@
         <v>23</v>
       </c>
       <c r="AI14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL14" t="n">
         <v>13</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO14" t="n">
         <v>1</v>
@@ -2962,7 +3029,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
@@ -2971,13 +3038,13 @@
         <v>13</v>
       </c>
       <c r="AT14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW14" t="n">
         <v>8</v>
@@ -2998,7 +3065,7 @@
         <v>2</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -3027,28 +3094,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
         <v>36</v>
       </c>
       <c r="G15" t="n">
-        <v>0.345</v>
+        <v>0.333</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
         <v>84</v>
       </c>
       <c r="K15" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L15" t="n">
         <v>9.199999999999999</v>
@@ -3057,22 +3124,22 @@
         <v>24.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O15" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P15" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R15" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S15" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T15" t="n">
         <v>42.2</v>
@@ -3081,7 +3148,7 @@
         <v>23.3</v>
       </c>
       <c r="V15" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W15" t="n">
         <v>6.7</v>
@@ -3090,7 +3157,7 @@
         <v>5.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z15" t="n">
         <v>20.1</v>
@@ -3102,19 +3169,19 @@
         <v>100.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.3</v>
+        <v>-5.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF15" t="n">
         <v>25</v>
       </c>
       <c r="AG15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
@@ -3129,13 +3196,13 @@
         <v>20</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO15" t="n">
         <v>19</v>
@@ -3150,13 +3217,13 @@
         <v>24</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
         <v>20</v>
@@ -3168,7 +3235,7 @@
         <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
         <v>9</v>
@@ -3177,7 +3244,7 @@
         <v>27</v>
       </c>
       <c r="BB15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16" t="n">
         <v>23</v>
       </c>
       <c r="G16" t="n">
-        <v>0.574</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J16" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0.456</v>
@@ -3242,25 +3309,25 @@
         <v>0.345</v>
       </c>
       <c r="O16" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P16" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.752</v>
+        <v>0.75</v>
       </c>
       <c r="R16" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S16" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T16" t="n">
         <v>42.4</v>
       </c>
       <c r="U16" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V16" t="n">
         <v>13.5</v>
@@ -3275,19 +3342,19 @@
         <v>5.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>94.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3308,7 +3375,7 @@
         <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3329,7 +3396,7 @@
         <v>20</v>
       </c>
       <c r="AR16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS16" t="n">
         <v>22</v>
@@ -3341,28 +3408,28 @@
         <v>15</v>
       </c>
       <c r="AV16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
         <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
         <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB16" t="n">
         <v>27</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3481,7 +3548,7 @@
         <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI17" t="n">
         <v>4</v>
@@ -3502,7 +3569,7 @@
         <v>10</v>
       </c>
       <c r="AO17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV17" t="n">
         <v>17</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,7 +3730,7 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI18" t="n">
         <v>29</v>
@@ -3681,7 +3748,7 @@
         <v>17</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO18" t="n">
         <v>28</v>
@@ -3702,7 +3769,7 @@
         <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV18" t="n">
         <v>21</v>
@@ -3723,7 +3790,7 @@
         <v>17</v>
       </c>
       <c r="BB18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>3.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
         <v>14</v>
@@ -3845,7 +3912,7 @@
         <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
         <v>10</v>
@@ -3863,7 +3930,7 @@
         <v>12</v>
       </c>
       <c r="AN19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3884,7 +3951,7 @@
         <v>3</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -3937,22 +4004,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E20" t="n">
         <v>23</v>
       </c>
       <c r="F20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" t="n">
-        <v>0.426</v>
+        <v>0.434</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
       </c>
       <c r="I20" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J20" t="n">
         <v>83.40000000000001</v>
@@ -3964,64 +4031,64 @@
         <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0.383</v>
+        <v>0.382</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="P20" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R20" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S20" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T20" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U20" t="n">
         <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W20" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X20" t="n">
         <v>6.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
         <v>22.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.2</v>
+        <v>99.5</v>
       </c>
       <c r="AC20" t="n">
         <v>-1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
       </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG20" t="n">
         <v>20</v>
@@ -4033,10 +4100,10 @@
         <v>13</v>
       </c>
       <c r="AJ20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
         <v>27</v>
@@ -4048,7 +4115,7 @@
         <v>2</v>
       </c>
       <c r="AO20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP20" t="n">
         <v>18</v>
@@ -4057,13 +4124,13 @@
         <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS20" t="n">
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AU20" t="n">
         <v>16</v>
@@ -4072,7 +4139,7 @@
         <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
         <v>1</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -4119,55 +4186,55 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E21" t="n">
         <v>21</v>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G21" t="n">
-        <v>0.382</v>
+        <v>0.389</v>
       </c>
       <c r="H21" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J21" t="n">
-        <v>83.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>0.444</v>
       </c>
       <c r="L21" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="M21" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.368</v>
+        <v>0.366</v>
       </c>
       <c r="O21" t="n">
         <v>14.8</v>
       </c>
       <c r="P21" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.748</v>
+        <v>0.749</v>
       </c>
       <c r="R21" t="n">
         <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U21" t="n">
         <v>20.4</v>
@@ -4191,13 +4258,13 @@
         <v>19.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.7</v>
+        <v>97.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.8</v>
+        <v>-1.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
@@ -4209,13 +4276,13 @@
         <v>23</v>
       </c>
       <c r="AH21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AI21" t="n">
         <v>20</v>
       </c>
       <c r="AJ21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK21" t="n">
         <v>19</v>
@@ -4227,7 +4294,7 @@
         <v>6</v>
       </c>
       <c r="AN21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4257,7 +4324,7 @@
         <v>14</v>
       </c>
       <c r="AX21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY21" t="n">
         <v>4</v>
@@ -4269,10 +4336,10 @@
         <v>22</v>
       </c>
       <c r="BB21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4397,7 +4464,7 @@
         <v>6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4409,7 +4476,7 @@
         <v>18</v>
       </c>
       <c r="AN22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4436,7 +4503,7 @@
         <v>27</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -4483,61 +4550,61 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F23" t="n">
         <v>40</v>
       </c>
       <c r="G23" t="n">
-        <v>0.298</v>
+        <v>0.286</v>
       </c>
       <c r="H23" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="I23" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="J23" t="n">
-        <v>82.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.352</v>
+        <v>0.349</v>
       </c>
       <c r="O23" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P23" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.762</v>
+        <v>0.76</v>
       </c>
       <c r="R23" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T23" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U23" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="V23" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W23" t="n">
         <v>7.6</v>
@@ -4555,10 +4622,10 @@
         <v>18.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.1</v>
+        <v>-5.4</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4573,10 +4640,10 @@
         <v>28</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AI23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ23" t="n">
         <v>18</v>
@@ -4591,28 +4658,28 @@
         <v>20</v>
       </c>
       <c r="AN23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP23" t="n">
         <v>22</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR23" t="n">
         <v>25</v>
       </c>
       <c r="AS23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT23" t="n">
         <v>23</v>
       </c>
       <c r="AU23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV23" t="n">
         <v>12</v>
@@ -4621,7 +4688,7 @@
         <v>15</v>
       </c>
       <c r="AX23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY23" t="n">
         <v>26</v>
@@ -4630,7 +4697,7 @@
         <v>8</v>
       </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB23" t="n">
         <v>24</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>0.268</v>
+        <v>0.273</v>
       </c>
       <c r="H24" t="n">
         <v>48.6</v>
@@ -4683,7 +4750,7 @@
         <v>38.3</v>
       </c>
       <c r="J24" t="n">
-        <v>88.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="K24" t="n">
         <v>0.434</v>
@@ -4692,28 +4759,28 @@
         <v>6.8</v>
       </c>
       <c r="M24" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.31</v>
+        <v>0.313</v>
       </c>
       <c r="O24" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="P24" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q24" t="n">
         <v>0.715</v>
       </c>
       <c r="R24" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S24" t="n">
-        <v>32.3</v>
+        <v>32.6</v>
       </c>
       <c r="T24" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
       <c r="U24" t="n">
         <v>22.1</v>
@@ -4722,10 +4789,10 @@
         <v>17.4</v>
       </c>
       <c r="W24" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y24" t="n">
         <v>7.4</v>
@@ -4737,25 +4804,25 @@
         <v>20.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="AC24" t="n">
         <v>-10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
       </c>
       <c r="AF24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG24" t="n">
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI24" t="n">
         <v>11</v>
@@ -4773,25 +4840,25 @@
         <v>15</v>
       </c>
       <c r="AN24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO24" t="n">
         <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
         <v>14</v>
       </c>
       <c r="AT24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU24" t="n">
         <v>12</v>
@@ -4812,7 +4879,7 @@
         <v>22</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB24" t="n">
         <v>16</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -4847,52 +4914,52 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E25" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F25" t="n">
         <v>21</v>
       </c>
       <c r="G25" t="n">
-        <v>0.611</v>
+        <v>0.604</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J25" t="n">
         <v>84.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L25" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M25" t="n">
         <v>25.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.368</v>
+        <v>0.371</v>
       </c>
       <c r="O25" t="n">
         <v>18.5</v>
       </c>
       <c r="P25" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.761</v>
+        <v>0.763</v>
       </c>
       <c r="R25" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S25" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T25" t="n">
         <v>43.6</v>
@@ -4910,25 +4977,25 @@
         <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z25" t="n">
         <v>22.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB25" t="n">
         <v>105</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF25" t="n">
         <v>8</v>
@@ -4940,13 +5007,13 @@
         <v>19</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
         <v>9</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL25" t="n">
         <v>1</v>
@@ -4955,16 +5022,16 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
         <v>10</v>
       </c>
       <c r="AP25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
         <v>12</v>
@@ -4979,22 +5046,22 @@
         <v>30</v>
       </c>
       <c r="AV25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW25" t="n">
         <v>9</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BB25" t="n">
         <v>5</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -5029,49 +5096,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E26" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F26" t="n">
         <v>18</v>
       </c>
       <c r="G26" t="n">
-        <v>0.673</v>
+        <v>0.667</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="J26" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L26" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="M26" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O26" t="n">
         <v>19</v>
       </c>
       <c r="P26" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.82</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S26" t="n">
         <v>33.4</v>
@@ -5080,43 +5147,43 @@
         <v>46.1</v>
       </c>
       <c r="U26" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V26" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="X26" t="n">
         <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
         <v>19.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>107.8</v>
+        <v>107.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF26" t="n">
         <v>5</v>
       </c>
       <c r="AG26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH26" t="n">
         <v>15</v>
@@ -5128,7 +5195,7 @@
         <v>2</v>
       </c>
       <c r="AK26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AL26" t="n">
         <v>2</v>
@@ -5137,19 +5204,19 @@
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO26" t="n">
         <v>6</v>
       </c>
       <c r="AP26" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS26" t="n">
         <v>6</v>
@@ -5167,16 +5234,16 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -5289,16 +5356,16 @@
         <v>-2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF27" t="n">
         <v>25</v>
       </c>
       <c r="AG27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH27" t="n">
         <v>10</v>
@@ -5307,7 +5374,7 @@
         <v>19</v>
       </c>
       <c r="AJ27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK27" t="n">
         <v>18</v>
@@ -5328,10 +5395,10 @@
         <v>4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS27" t="n">
         <v>17</v>
@@ -5349,7 +5416,7 @@
         <v>21</v>
       </c>
       <c r="AX27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY27" t="n">
         <v>24</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -5393,67 +5460,67 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E28" t="n">
         <v>40</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>0.714</v>
+        <v>0.727</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>40.2</v>
+        <v>40.4</v>
       </c>
       <c r="J28" t="n">
         <v>82.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.488</v>
+        <v>0.49</v>
       </c>
       <c r="L28" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="M28" t="n">
         <v>20.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0.388</v>
+        <v>0.393</v>
       </c>
       <c r="O28" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="P28" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.778</v>
+        <v>0.775</v>
       </c>
       <c r="R28" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="S28" t="n">
         <v>33.4</v>
       </c>
       <c r="T28" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U28" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="V28" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W28" t="n">
         <v>7.4</v>
       </c>
       <c r="X28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y28" t="n">
         <v>4.8</v>
@@ -5465,13 +5532,13 @@
         <v>19.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.8</v>
+        <v>104.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5495,7 +5562,7 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AM28" t="n">
         <v>19</v>
@@ -5504,13 +5571,13 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP28" t="n">
         <v>29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
@@ -5519,22 +5586,22 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
         <v>18</v>
       </c>
       <c r="AX28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ28" t="n">
         <v>2</v>
@@ -5543,10 +5610,10 @@
         <v>24</v>
       </c>
       <c r="BB28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -5575,31 +5642,31 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F29" t="n">
         <v>25</v>
       </c>
       <c r="G29" t="n">
-        <v>0.545</v>
+        <v>0.537</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J29" t="n">
-        <v>82.7</v>
+        <v>82.5</v>
       </c>
       <c r="K29" t="n">
         <v>0.439</v>
       </c>
       <c r="L29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>22.8</v>
@@ -5608,13 +5675,13 @@
         <v>0.362</v>
       </c>
       <c r="O29" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P29" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R29" t="n">
         <v>11.9</v>
@@ -5626,10 +5693,10 @@
         <v>42.9</v>
       </c>
       <c r="U29" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V29" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W29" t="n">
         <v>7</v>
@@ -5647,13 +5714,13 @@
         <v>21.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5665,7 +5732,7 @@
         <v>12</v>
       </c>
       <c r="AH29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
         <v>25</v>
@@ -5689,10 +5756,10 @@
         <v>7</v>
       </c>
       <c r="AP29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR29" t="n">
         <v>10</v>
@@ -5701,13 +5768,13 @@
         <v>21</v>
       </c>
       <c r="AT29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW29" t="n">
         <v>25</v>
@@ -5716,7 +5783,7 @@
         <v>22</v>
       </c>
       <c r="AY29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ29" t="n">
         <v>29</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E30" t="n">
         <v>19</v>
       </c>
       <c r="F30" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G30" t="n">
-        <v>0.352</v>
+        <v>0.358</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
@@ -5784,34 +5851,34 @@
         <v>6.7</v>
       </c>
       <c r="M30" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O30" t="n">
         <v>16.3</v>
       </c>
       <c r="P30" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R30" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S30" t="n">
         <v>30.8</v>
       </c>
       <c r="T30" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U30" t="n">
         <v>20</v>
       </c>
       <c r="V30" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W30" t="n">
         <v>6.9</v>
@@ -5820,7 +5887,7 @@
         <v>4.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z30" t="n">
         <v>20.8</v>
@@ -5832,10 +5899,10 @@
         <v>94.40000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>-6</v>
+        <v>-5.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE30" t="n">
         <v>24</v>
@@ -5850,13 +5917,13 @@
         <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ30" t="n">
         <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="n">
         <v>23</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="n">
         <v>24</v>
@@ -5880,7 +5947,7 @@
         <v>17</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
         <v>24</v>
@@ -5889,16 +5956,16 @@
         <v>28</v>
       </c>
       <c r="AV30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW30" t="n">
         <v>26</v>
       </c>
       <c r="AX30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ30" t="n">
         <v>18</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6038,7 +6105,7 @@
         <v>8</v>
       </c>
       <c r="AK31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL31" t="n">
         <v>15</v>
@@ -6050,13 +6117,13 @@
         <v>3</v>
       </c>
       <c r="AO31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP31" t="n">
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR31" t="n">
         <v>20</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-21-2013-14</t>
+          <t>2014-02-21</t>
         </is>
       </c>
     </row>
